--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_27.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_27.xlsx
@@ -1,39 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224DFB0B-4372-4401-97C8-FA4F5A966915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3F7C85-F734-4C98-898A-113B70E42B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9972" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowCCNoCF" sheetId="6" r:id="rId1"/>
-    <sheet name="PayNowCC_27" sheetId="1" r:id="rId2"/>
-    <sheet name="VerifyPaymentConfPayNowCC" sheetId="21" r:id="rId3"/>
-    <sheet name="ModifyPaymentsCC1" sheetId="15" r:id="rId4"/>
-    <sheet name="ModifyPaymentsCC2" sheetId="16" r:id="rId5"/>
-    <sheet name="NoModifyAmountCC" sheetId="17" r:id="rId6"/>
-    <sheet name="NoModifyBillingAddressCC" sheetId="18" r:id="rId7"/>
-    <sheet name="PayNowSCFCC_27" sheetId="2" r:id="rId8"/>
-    <sheet name="SCFCCVerbiage" sheetId="20" r:id="rId9"/>
-    <sheet name="PayNowDCFCC_27" sheetId="3" r:id="rId10"/>
-    <sheet name="DCFCCVerbiage" sheetId="19" r:id="rId11"/>
-    <sheet name="CCDeferredCC_27" sheetId="4" r:id="rId12"/>
-    <sheet name="CMCAutopayCC_27" sheetId="5" r:id="rId13"/>
-    <sheet name="CancelStaticTextAutopayCC" sheetId="7" r:id="rId14"/>
-    <sheet name="CancelSuccessAutopayCC" sheetId="8" r:id="rId15"/>
-    <sheet name="CancelStaticTextDeferredCC" sheetId="9" r:id="rId16"/>
-    <sheet name="CancelSuccessDeferredCC" sheetId="10" r:id="rId17"/>
-    <sheet name="ModifyStaticTextAutopayCC" sheetId="11" r:id="rId18"/>
-    <sheet name="ModifySuccessAutopayCC" sheetId="12" r:id="rId19"/>
-    <sheet name="ModifyStaticTextDeferredCC" sheetId="13" r:id="rId20"/>
-    <sheet name="ModifySuccessDeferredCC" sheetId="14" r:id="rId21"/>
+    <sheet name="PayNowCC_27" sheetId="1" r:id="rId1"/>
+    <sheet name="VerifyPaymentConfPayNowCC" sheetId="21" r:id="rId2"/>
+    <sheet name="ModifyPaymentsCC1" sheetId="15" r:id="rId3"/>
+    <sheet name="ModifyPaymentsCC2" sheetId="16" r:id="rId4"/>
+    <sheet name="NoModifyAmountCC" sheetId="17" r:id="rId5"/>
+    <sheet name="NoModifyBillingAddressCC" sheetId="18" r:id="rId6"/>
+    <sheet name="PayNowSCFCC_27" sheetId="2" r:id="rId7"/>
+    <sheet name="SCFCCVerbiage" sheetId="20" r:id="rId8"/>
+    <sheet name="PayNowDCFCC_27" sheetId="3" r:id="rId9"/>
+    <sheet name="DCFCCVerbiage" sheetId="19" r:id="rId10"/>
+    <sheet name="CCDeferredCC_27" sheetId="4" r:id="rId11"/>
+    <sheet name="CMCAutopayCC_27" sheetId="5" r:id="rId12"/>
+    <sheet name="CancelStaticTextAutopayCC" sheetId="7" r:id="rId13"/>
+    <sheet name="CancelSuccessAutopayCC" sheetId="8" r:id="rId14"/>
+    <sheet name="CancelStaticTextDeferredCC" sheetId="9" r:id="rId15"/>
+    <sheet name="CancelSuccessDeferredCC" sheetId="10" r:id="rId16"/>
+    <sheet name="ModifyStaticTextAutopayCC" sheetId="11" r:id="rId17"/>
+    <sheet name="ModifySuccessAutopayCC" sheetId="12" r:id="rId18"/>
+    <sheet name="ModifyStaticTextDeferredCC" sheetId="13" r:id="rId19"/>
+    <sheet name="ModifySuccessDeferredCC" sheetId="14" r:id="rId20"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="59">
   <si>
     <t>Result</t>
   </si>
@@ -140,12 +139,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sat May 30 00:53:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat May 30 01:02:50 IST 2026</t>
-  </si>
-  <si>
     <t>Sat May 30 01:14:09 IST 2026</t>
   </si>
   <si>
@@ -170,15 +163,9 @@
     <t>Sat May 30 02:04:44 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jun 01 19:59:06 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jun 01 20:09:33 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jun 01 20:15:03 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jun 01 20:34:54 IST 2026</t>
   </si>
   <si>
@@ -191,9 +178,6 @@
     <t>Mon Jun 01 21:14:39 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 20:28:39 IST 2026</t>
-  </si>
-  <si>
     <t>6427</t>
   </si>
   <si>
@@ -203,13 +187,40 @@
     <t>6429</t>
   </si>
   <si>
-    <t>Fri Jul 17 20:50:43 IST 2026</t>
-  </si>
-  <si>
     <t>6430</t>
   </si>
   <si>
-    <t>Fri Jul 17 21:06:23 IST 2026</t>
+    <t>Tue Aug 25 21:26:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 21:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 19:18:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 19:24:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 19:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 20:15:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 20:23:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 20:32:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Aug 26 22:31:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 19:17:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 19:43:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -546,7 +557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7A018-07CA-4DE2-85D2-C45310919A6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -599,7 +610,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -609,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -636,104 +647,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14611B2-272D-4F6C-A3A3-34625CF21E5C}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF4BB81-CC08-4091-9D95-3A4A11E173EE}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -787,7 +707,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -827,7 +747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924AD824-C93A-4DEC-A40B-651CCF250E75}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -884,7 +804,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -894,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -926,7 +846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26DA0F3-1CAA-4554-B84A-57402F442697}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -980,7 +900,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -990,7 +910,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1018,7 +938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6859EFA-971B-46EF-9F88-19ADA00CDDC2}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1072,7 +992,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1082,7 +1002,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1110,7 +1030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B4F343-DA62-4980-9834-419A05CC33C3}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1164,7 +1084,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1174,7 +1094,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1202,7 +1122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8C958B-BC9A-44BC-84D9-4487E068BDBA}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1259,7 +1179,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1269,7 +1189,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1301,7 +1221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD46E377-6BD6-4BA8-BB7B-7095CAEE12C3}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1358,7 +1278,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1368,7 +1288,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1400,7 +1320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502AF05A-5E83-4891-B6D4-3A99DCDD7B93}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1454,7 +1374,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1464,7 +1384,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1492,7 +1412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D64F9E7-8E19-4FF9-858F-B27AAD9E9DD1}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1546,7 +1466,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1556,7 +1476,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1584,104 +1504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FF5417-5A97-4FF0-B4A6-4CB3ACCC5E12}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1738,7 +1561,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1748,7 +1571,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1780,7 +1603,101 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F387F6-118B-48DC-9C79-B9D10422FE4D}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4A1512-11EF-4F9D-8705-BB77A40DA376}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1837,7 +1754,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1847,7 +1764,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -1880,100 +1797,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F387F6-118B-48DC-9C79-B9D10422FE4D}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122661BC-EB0E-415D-9F4C-17C6AACD5339}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2061,7 +1884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00532F1A-916F-4150-88F2-B68490CEFE46}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2149,7 +1972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D345C4-0731-4594-B067-756A7E19A715}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2200,10 +2023,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2213,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -2241,7 +2064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BA9A57-C3C6-46D0-A1CE-2333157B7279}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2295,7 +2118,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2305,7 +2128,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -2333,7 +2156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A599422F-DB1C-494D-AC7A-FABC7A55F2B3}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2384,10 +2207,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2397,7 +2220,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
@@ -2427,7 +2250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C8C373-558A-4744-952F-549562AC4B84}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2481,7 +2304,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2492,6 +2315,100 @@
       </c>
       <c r="F2" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14611B2-272D-4F6C-A3A3-34625CF21E5C}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>16</v>
